--- a/dist/script_m1.xlsx
+++ b/dist/script_m1.xlsx
@@ -865,12 +865,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ الدَّائِرَةَ وَالمُرَبَّعَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ الدَّائِرَةَ وَالمُرَبَّعَ.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ الدَّائِرَةَ وَالمُرَبَّعَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ الدَّائِرَةَ وَالمُرَبَّعَ.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ المُثَلَّثَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ المُثَلَّثَ.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ المُثَلَّثَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ المُثَلَّثَ.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ المُسْتَطِيلَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ المُسْتَطِيلَ.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ المُسْتَطِيلَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ المُسْتَطِيلَ.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ صَيْدَ الأَشْكَالِ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ صَيْدَ الأَشْكَالِ.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ صَيْدَ الأَشْكَالِ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ صَيْدَ الأَشْكَالِ.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ المُكَعَّبَ وَالكُرَةَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ المُكَعَّبَ وَالكُرَةَ.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ المُكَعَّبَ وَالكُرَةَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ المُكَعَّبَ وَالكُرَةَ.</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ الأُسْطُوَانَةَ وَالمَخْرُوطَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ الأُسْطُوَانَةَ وَالمَخْرُوطَ.</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ الأُسْطُوَانَةَ وَالمَخْرُوطَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ الأُسْطُوَانَةَ وَالمَخْرُوطَ.</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتَ المُسَطَّحَ وَالمُجَسَّمَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتَ المُسَطَّحَ وَالمُجَسَّمَ.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>ثَلَاثَةٌ مِنْ ثَلَاثَةٍ! أَتْقَنْتِ المُسَطَّحَ وَالمُجَسَّمَ.</t>
+          <t>رَائِعٌ! أَتْقَنْتِ المُسَطَّحَ وَالمُجَسَّمَ.</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
